--- a/Data/g13.6.xlsx
+++ b/Data/g13.6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,7 +713,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -723,11 +723,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01/10/2012</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="16">
@@ -743,11 +743,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01/10/2013</t>
+          <t>01/10/2012</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="17">
@@ -763,11 +763,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01/10/2014</t>
+          <t>01/10/2013</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -783,11 +783,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2014</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -803,11 +803,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="20">
@@ -823,11 +823,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="21">
@@ -843,11 +843,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -863,11 +863,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="23">
@@ -883,11 +883,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="24">
@@ -903,7 +903,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -923,11 +923,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -943,11 +943,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="27">
@@ -963,17 +963,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01/10/2024</t>
+          <t>01/10/2023</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8.699999999999999</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/10/2012</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.699999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1003,11 +1003,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01/10/2013</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="30">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01/10/2014</t>
+          <t>01/10/2012</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1043,11 +1043,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01/10/2015</t>
+          <t>01/10/2013</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01/10/2016</t>
+          <t>01/10/2014</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="33">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01/10/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.7</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="34">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/10/2018</t>
+          <t>01/10/2016</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1123,11 +1123,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/10/2019</t>
+          <t>01/10/2017</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="36">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/10/2018</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="37">
@@ -1163,11 +1163,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>01/10/2019</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="38">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1223,11 +1223,71 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>01/10/2022</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Taxa de desocupação, na semana de referência, das pessoas de 14 anos ou mais de idade</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>01/10/2023</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Taxa de desocupação, na semana de referência, das pessoas de 14 anos ou mais de idade</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>01/10/2024</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D42" t="n">
         <v>8.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Taxa de desocupação, na semana de referência, das pessoas de 14 anos ou mais de idade</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
